--- a/CODES.xlsx
+++ b/CODES.xlsx
@@ -1145,7 +1145,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L0660]</t>
+          <t xml:space="preserve">[L0679]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,21 +1157,21 @@
         <v>6</v>
       </c>
       <c r="D27">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">h2</t>
+          <t xml:space="preserve">p</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heading</t>
+          <t xml:space="preserve">Body / paragraph</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recent dispatches</t>
+          <t xml:space="preserve">Subscribe</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1181,14 +1181,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">RD001</t>
+          <t xml:space="preserve">CS001</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L7861]</t>
+          <t xml:space="preserve">[L0680]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1197,24 +1197,24 @@
         </is>
       </c>
       <c r="C28">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="D28">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">a</t>
+          <t xml:space="preserve">h2</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link</t>
+          <t xml:space="preserve">Heading</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Browse the archive →</t>
+          <t xml:space="preserve">Get the next issue of the Guide to Infrastructure.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1224,14 +1224,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">RD002</t>
+          <t xml:space="preserve">CS002</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L0664]</t>
+          <t xml:space="preserve">[L5380]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1240,24 +1240,24 @@
         </is>
       </c>
       <c r="C29">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="D29">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">input</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Input placeholder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grid</t>
+          <t xml:space="preserve">you@example.com</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1267,14 +1267,14 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">RD010</t>
+          <t xml:space="preserve">CS003</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L3664]</t>
+          <t xml:space="preserve">[L5383]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="C30">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D30">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Water</t>
+          <t xml:space="preserve">Free. One issue a fortnight. Unsubscribe whenever.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1310,14 +1310,14 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">RD020</t>
+          <t xml:space="preserve">CS005</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L6664]</t>
+          <t xml:space="preserve">[L5690]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="C31">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D31">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transit</t>
+          <t xml:space="preserve">Read</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1353,14 +1353,14 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">RD030</t>
+          <t xml:space="preserve">FT002</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L0665]</t>
+          <t xml:space="preserve">[L7690]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1369,24 +1369,24 @@
         </is>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="D32">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">h3</t>
+          <t xml:space="preserve">p</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subheading</t>
+          <t xml:space="preserve">Body / paragraph</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">The pylon that got a paint job and a fan club</t>
+          <t xml:space="preserve">Elsewhere</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1396,14 +1396,14 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RD011</t>
+          <t xml:space="preserve">FT006</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L3665]</t>
+          <t xml:space="preserve">[L5691]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1412,24 +1412,24 @@
         </is>
       </c>
       <c r="C33">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D33">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">h3</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subheading</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">In defence of the visible drainpipe</t>
+          <t xml:space="preserve">Latest issue</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1439,14 +1439,14 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">RD021</t>
+          <t xml:space="preserve">FT003</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L6665]</t>
+          <t xml:space="preserve">[L7691]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1455,24 +1455,24 @@
         </is>
       </c>
       <c r="C34">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D34">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">h3</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subheading</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">A ventilation shaft with a sense of occasion</t>
+          <t xml:space="preserve">Newsletter</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1482,14 +1482,14 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">RD031</t>
+          <t xml:space="preserve">FT007</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L3666]</t>
+          <t xml:space="preserve">[L0692]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="C35">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="D35">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aug 10 · 7 min</t>
+          <t xml:space="preserve">Infrastructure, styled to be seen. A fortnightly field guide to the built world.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1525,14 +1525,14 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">RD022</t>
+          <t xml:space="preserve">FT001</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L0667]</t>
+          <t xml:space="preserve">[L5692]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1541,24 +1541,24 @@
         </is>
       </c>
       <c r="C36">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="D36">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aug 24 · 6 min</t>
+          <t xml:space="preserve">Archive</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1568,14 +1568,14 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">RD012</t>
+          <t xml:space="preserve">FT004</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L6667]</t>
+          <t xml:space="preserve">[L7692]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1584,24 +1584,24 @@
         </is>
       </c>
       <c r="C37">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D37">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jul 27 · 9 min</t>
+          <t xml:space="preserve">Instagram</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1611,14 +1611,14 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">RD032</t>
+          <t xml:space="preserve">FT008</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L0670]</t>
+          <t xml:space="preserve">[L7693]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1627,24 +1627,24 @@
         </is>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="D38">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data</t>
+          <t xml:space="preserve">Contact</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1654,14 +1654,14 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">RD040</t>
+          <t xml:space="preserve">FT009</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L3670]</t>
+          <t xml:space="preserve">[L0696]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1670,24 +1670,24 @@
         </is>
       </c>
       <c r="C39">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="D39">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">span</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Text</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roads</t>
+          <t xml:space="preserve">© 2026 ESUNOS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1697,14 +1697,14 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">RD050</t>
+          <t xml:space="preserve">FT010</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L6670]</t>
+          <t xml:space="preserve">[L8696]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1713,24 +1713,24 @@
         </is>
       </c>
       <c r="C40">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="D40">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">span</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Text</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Field notes</t>
+          <t xml:space="preserve">esunos.com</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1740,40 +1740,40 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">RD060</t>
+          <t xml:space="preserve">FT011</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L0671]</t>
+          <t xml:space="preserve">[I0000]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing</t>
+          <t xml:space="preserve">Issue 01</t>
         </is>
       </c>
       <c r="C41">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">h3</t>
+          <t xml:space="preserve">title</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subheading</t>
+          <t xml:space="preserve">Title (SEO)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Server halls are the new industrial sublime</t>
+          <t xml:space="preserve">Why the substation became a landmark — ESUNOS Issue 01</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1783,40 +1783,40 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">RD041</t>
+          <t xml:space="preserve">IM001</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L3671]</t>
+          <t xml:space="preserve">[I0600]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing</t>
+          <t xml:space="preserve">Issue 01</t>
         </is>
       </c>
       <c r="C42">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="D42">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">h3</t>
+          <t xml:space="preserve">span</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subheading</t>
+          <t xml:space="preserve">Text</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">The gantry as public sculpture</t>
+          <t xml:space="preserve">The ESUNOS Guide to Infrastructure</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1826,40 +1826,40 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">RD051</t>
+          <t xml:space="preserve">HD001</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L6671]</t>
+          <t xml:space="preserve">[I7800]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing</t>
+          <t xml:space="preserve">Issue 01</t>
         </is>
       </c>
       <c r="C43">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D43">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">h3</t>
+          <t xml:space="preserve">span</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subheading</t>
+          <t xml:space="preserve">Text</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reading a city by its manhole covers</t>
+          <t xml:space="preserve">Issue 01 — September 2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1869,40 +1869,40 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">RD061</t>
+          <t xml:space="preserve">HD002</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L3672]</t>
+          <t xml:space="preserve">[I0001]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing</t>
+          <t xml:space="preserve">Issue 01</t>
         </is>
       </c>
       <c r="C44">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">meta</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Meta description</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jun 29 · 5 min</t>
+          <t xml:space="preserve">For a century the grid hid in the hedges. Three engineers decided it should be the view instead. The ESUNOS Guide to Infrastructure, Issue 01.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1912,40 +1912,40 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">RD052</t>
+          <t xml:space="preserve">IM002</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L6672]</t>
+          <t xml:space="preserve">[I6201]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing</t>
+          <t xml:space="preserve">Issue 01</t>
         </is>
       </c>
       <c r="C45">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D45">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jun 15 · 6 min</t>
+          <t xml:space="preserve">Home</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -1955,40 +1955,40 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">RD062</t>
+          <t xml:space="preserve">HD004</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L0673]</t>
+          <t xml:space="preserve">[I6801]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing</t>
+          <t xml:space="preserve">Issue 01</t>
         </is>
       </c>
       <c r="C46">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="D46">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jul 13 · 8 min</t>
+          <t xml:space="preserve">Archive</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1998,40 +1998,40 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">RD042</t>
+          <t xml:space="preserve">HD006</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L0679]</t>
+          <t xml:space="preserve">[I7601]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing</t>
+          <t xml:space="preserve">Issue 01</t>
         </is>
       </c>
       <c r="C47">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="D47">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subscribe</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2041,40 +2041,40 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">CS001</t>
+          <t xml:space="preserve">HD007</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L0680]</t>
+          <t xml:space="preserve">[I2504]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing</t>
+          <t xml:space="preserve">Issue 01</t>
         </is>
       </c>
       <c r="C48">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D48">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">h2</t>
+          <t xml:space="preserve">span</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heading</t>
+          <t xml:space="preserve">Text</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get the next issue of the Guide to Infrastructure.</t>
+          <t xml:space="preserve">Feature 01</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2084,40 +2084,40 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">CS002</t>
+          <t xml:space="preserve">AH001</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L5380]</t>
+          <t xml:space="preserve">[I3404]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing</t>
+          <t xml:space="preserve">Issue 01</t>
         </is>
       </c>
       <c r="C49">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D49">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">input</t>
+          <t xml:space="preserve">span</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Input placeholder</t>
+          <t xml:space="preserve">Text</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">you@example.com</t>
+          <t xml:space="preserve">Grid · Power</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2127,40 +2127,40 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">CS003</t>
+          <t xml:space="preserve">AH002</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L5383]</t>
+          <t xml:space="preserve">[I2505]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing</t>
+          <t xml:space="preserve">Issue 01</t>
         </is>
       </c>
       <c r="C50">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="D50">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">h1</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Page title</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Free. One issue a fortnight. Unsubscribe whenever.</t>
+          <t xml:space="preserve">Why the substation became a landmark</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2170,26 +2170,26 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">CS005</t>
+          <t xml:space="preserve">AH003</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L5690]</t>
+          <t xml:space="preserve">[I2508]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing</t>
+          <t xml:space="preserve">Issue 01</t>
         </is>
       </c>
       <c r="C51">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="D51">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Read</t>
+          <t xml:space="preserve">For a century the grid hid in the hedges. Three engineers decided it should be the view instead.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2213,40 +2213,40 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">FT002</t>
+          <t xml:space="preserve">AH004</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L7690]</t>
+          <t xml:space="preserve">[I2511]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing</t>
+          <t xml:space="preserve">Issue 01</t>
         </is>
       </c>
       <c r="C52">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="D52">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">div</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">div</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsewhere</t>
+          <t xml:space="preserve">PHOTO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2256,40 +2256,40 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">FT006</t>
+          <t xml:space="preserve">PH004</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L5691]</t>
+          <t xml:space="preserve">[I3011]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing</t>
+          <t xml:space="preserve">Issue 01</t>
         </is>
       </c>
       <c r="C53">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="D53">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">a</t>
+          <t xml:space="preserve">div</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link</t>
+          <t xml:space="preserve">div</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Latest issue</t>
+          <t xml:space="preserve">Hugo Sale</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2299,40 +2299,40 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">FT003</t>
+          <t xml:space="preserve">AH005</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L7691]</t>
+          <t xml:space="preserve">[I3012]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing</t>
+          <t xml:space="preserve">Issue 01</t>
         </is>
       </c>
       <c r="C54">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="D54">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">a</t>
+          <t xml:space="preserve">div</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link</t>
+          <t xml:space="preserve">div</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newsletter</t>
+          <t xml:space="preserve">September 21, 2026 · 11 min read</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2342,40 +2342,40 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">FT007</t>
+          <t xml:space="preserve">AH006</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L0692]</t>
+          <t xml:space="preserve">[I0826]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing</t>
+          <t xml:space="preserve">Issue 01</t>
         </is>
       </c>
       <c r="C55">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D55">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">figcaption</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Caption</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Infrastructure, styled to be seen. A fortnightly field guide to the built world.</t>
+          <t xml:space="preserve">[ Photograph: Battersea "A" substation, floodlit — full bleed ]</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2385,40 +2385,40 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">FT001</t>
+          <t xml:space="preserve">PH001</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L5692]</t>
+          <t xml:space="preserve">[I2528]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing</t>
+          <t xml:space="preserve">Issue 01</t>
         </is>
       </c>
       <c r="C56">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="D56">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">a</t>
+          <t xml:space="preserve">p</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link</t>
+          <t xml:space="preserve">Body / paragraph</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Archive</t>
+          <t xml:space="preserve">There is a moment, walking south from the river at dusk, when the substation stops looking like a warning and starts looking like a building. Its transformers hum behind a lattice of steel; a run of ceramic insulators catches the last of the light like a shelf of trophies. Nobody designed it to be beautiful. That, the engineers here will tell you, was the mistake worth fixing.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2428,40 +2428,40 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">FT004</t>
+          <t xml:space="preserve">AB001</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L7692]</t>
+          <t xml:space="preserve">[I2532]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing</t>
+          <t xml:space="preserve">Issue 01</t>
         </is>
       </c>
       <c r="C57">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="D57">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">a</t>
+          <t xml:space="preserve">p</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link</t>
+          <t xml:space="preserve">Body / paragraph</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instagram</t>
+          <t xml:space="preserve">Infrastructure has spent most of a century apologising for itself. We buried the cables, fenced the plant, and planted fast-growing conifers in front of anything that buzzed. The result is a built world we rely on completely and refuse to look at — a landscape of shrugging grey boxes designed, above all, to be ignored.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2471,40 +2471,40 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">FT008</t>
+          <t xml:space="preserve">AB002</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L7693]</t>
+          <t xml:space="preserve">[I2536]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing</t>
+          <t xml:space="preserve">Issue 01</t>
         </is>
       </c>
       <c r="C58">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="D58">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">a</t>
+          <t xml:space="preserve">h2</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link</t>
+          <t xml:space="preserve">Heading</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contact</t>
+          <t xml:space="preserve">The case for showing your working</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2514,40 +2514,40 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">FT009</t>
+          <t xml:space="preserve">AB010</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L0696]</t>
+          <t xml:space="preserve">[I2537]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing</t>
+          <t xml:space="preserve">Issue 01</t>
         </is>
       </c>
       <c r="C59">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D59">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">span</t>
+          <t xml:space="preserve">p</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Text</t>
+          <t xml:space="preserve">Body / paragraph</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">© 2026 ESUNOS</t>
+          <t xml:space="preserve">The counter-movement is small but loud. In three sites across the south-east, engineers and architects have started treating the grid as something to be seen — painting gantries, uplighting cooling towers, cutting viewing slots into perimeter walls. The bill is trivial next to the build. The change in how people treat the thing is not.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2557,40 +2557,40 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">FT010</t>
+          <t xml:space="preserve">AB003</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">[L8696]</t>
+          <t xml:space="preserve">[I2750]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing</t>
+          <t xml:space="preserve">Issue 01</t>
         </is>
       </c>
       <c r="C60">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="D60">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">span</t>
+          <t xml:space="preserve">figcaption</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Text</t>
+          <t xml:space="preserve">Caption</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">esunos.com</t>
+          <t xml:space="preserve">[ Photograph: uplit cooling tower, Greenwich reach ]</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2600,14 +2600,14 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">FT011</t>
+          <t xml:space="preserve">PH002</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I0000]</t>
+          <t xml:space="preserve">[I2552]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2616,24 +2616,24 @@
         </is>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">title</t>
+          <t xml:space="preserve">p</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Title (SEO)</t>
+          <t xml:space="preserve">Body / paragraph</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Why the substation became a landmark — ESUNOS Issue 01</t>
+          <t xml:space="preserve">"A fence says keep out. A good facade says look — and people did."</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2643,14 +2643,14 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">IM001</t>
+          <t xml:space="preserve">PQ001</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I0600]</t>
+          <t xml:space="preserve">[I2554]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2659,24 +2659,24 @@
         </is>
       </c>
       <c r="C62">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">span</t>
+          <t xml:space="preserve">cite</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Text</t>
+          <t xml:space="preserve">Citation</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ESUNOS Guide to Infrastructure</t>
+          <t xml:space="preserve">— Site engineer, Substation "A"</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2686,14 +2686,14 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">HD001</t>
+          <t xml:space="preserve">PQ002</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I7800]</t>
+          <t xml:space="preserve">[I2556]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2702,24 +2702,24 @@
         </is>
       </c>
       <c r="C63">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">span</t>
+          <t xml:space="preserve">p</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Text</t>
+          <t xml:space="preserve">Body / paragraph</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01 — September 2026</t>
+          <t xml:space="preserve">What surprised the operators was not the visitors — though there are now visitors — but the vandalism that stopped. A structure people find handsome is a structure people leave alone. Graffiti fell. Fly-tipping at the perimeter fell. The maintenance crews, oddly, reported taking more care too.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2729,14 +2729,14 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">HD002</t>
+          <t xml:space="preserve">AB004</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I0001]</t>
+          <t xml:space="preserve">[I2559]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2745,24 +2745,24 @@
         </is>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">meta</t>
+          <t xml:space="preserve">h2</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meta description</t>
+          <t xml:space="preserve">Heading</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">For a century the grid hid in the hedges. Three engineers decided it should be the view instead. The ESUNOS Guide to Infrastructure, Issue 01.</t>
+          <t xml:space="preserve">Three that got it right</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2772,14 +2772,14 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">IM002</t>
+          <t xml:space="preserve">AB011</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I6201]</t>
+          <t xml:space="preserve">[I2561]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2788,24 +2788,24 @@
         </is>
       </c>
       <c r="C65">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">a</t>
+          <t xml:space="preserve">p</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link</t>
+          <t xml:space="preserve">Body / paragraph</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home</t>
+          <t xml:space="preserve">Below, the shortlist from this issue's field trips — the full notes, drawings and a map are in the members' edition.</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2815,14 +2815,14 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">HD004</t>
+          <t xml:space="preserve">AB005</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I6801]</t>
+          <t xml:space="preserve">[I2963]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2831,24 +2831,24 @@
         </is>
       </c>
       <c r="C66">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">a</t>
+          <t xml:space="preserve">span</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link</t>
+          <t xml:space="preserve">Text</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Archive</t>
+          <t xml:space="preserve">Battersea "A" — floodlighting turned a maintenance liability into the neighbourhood's favourite skyline.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2858,14 +2858,14 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">HD006</t>
+          <t xml:space="preserve">LI001</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I7601]</t>
+          <t xml:space="preserve">[I2965]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2874,24 +2874,24 @@
         </is>
       </c>
       <c r="C67">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">a</t>
+          <t xml:space="preserve">span</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link</t>
+          <t xml:space="preserve">Text</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">About</t>
+          <t xml:space="preserve">Greenwich reach — a perimeter wall with viewing slots, so the plant reads as a colonnade.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2901,14 +2901,14 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">HD007</t>
+          <t xml:space="preserve">LI002</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I2504]</t>
+          <t xml:space="preserve">[I2967]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="C68">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D68">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feature 01</t>
+          <t xml:space="preserve">Kent interconnector — gantries painted a single confident orange, visible for miles.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2944,14 +2944,14 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">AH001</t>
+          <t xml:space="preserve">LI003</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I3404]</t>
+          <t xml:space="preserve">[I2779]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2960,24 +2960,24 @@
         </is>
       </c>
       <c r="C69">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>79</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">span</t>
+          <t xml:space="preserve">figcaption</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Text</t>
+          <t xml:space="preserve">Caption</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grid · Power</t>
+          <t xml:space="preserve">[ Photograph: Kent interconnector gantries, painted orange ]</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2987,14 +2987,14 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">AH002</t>
+          <t xml:space="preserve">PH003</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I2505]</t>
+          <t xml:space="preserve">[I2580]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3006,21 +3006,21 @@
         <v>25</v>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">h1</t>
+          <t xml:space="preserve">p</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Page title</t>
+          <t xml:space="preserve">Body / paragraph</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Why the substation became a landmark</t>
+          <t xml:space="preserve">None of it is complicated. That is rather the point. The technology of caring what infrastructure looks like is a century old; what was missing was permission. This issue is an argument that the permission is overdue.</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3030,14 +3030,14 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">AH003</t>
+          <t xml:space="preserve">AB006</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I2508]</t>
+          <t xml:space="preserve">[I0686]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3046,10 +3046,10 @@
         </is>
       </c>
       <c r="C71">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D71">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">For a century the grid hid in the hedges. Three engineers decided it should be the view instead.</t>
+          <t xml:space="preserve">Subscribe</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3073,14 +3073,14 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">AH004</t>
+          <t xml:space="preserve">SU001</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I2511]</t>
+          <t xml:space="preserve">[I0687]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3089,24 +3089,24 @@
         </is>
       </c>
       <c r="C72">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D72">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">div</t>
+          <t xml:space="preserve">h2</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">div</t>
+          <t xml:space="preserve">Heading</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">PHOTO</t>
+          <t xml:space="preserve">Get the next issue of the Guide to Infrastructure.</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3116,14 +3116,14 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">PH004</t>
+          <t xml:space="preserve">SU002</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I3011]</t>
+          <t xml:space="preserve">[I5387]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3132,24 +3132,24 @@
         </is>
       </c>
       <c r="C73">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="D73">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">div</t>
+          <t xml:space="preserve">input</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">div</t>
+          <t xml:space="preserve">Input placeholder</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hugo Sale</t>
+          <t xml:space="preserve">you@example.com</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3159,14 +3159,14 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">AH005</t>
+          <t xml:space="preserve">SU003</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I3012]</t>
+          <t xml:space="preserve">[I5389]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3175,24 +3175,24 @@
         </is>
       </c>
       <c r="C74">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="D74">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">div</t>
+          <t xml:space="preserve">p</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">div</t>
+          <t xml:space="preserve">Body / paragraph</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">September 21, 2026 · 11 min read</t>
+          <t xml:space="preserve">Free. One issue a fortnight. Unsubscribe whenever.</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3202,14 +3202,14 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">AH006</t>
+          <t xml:space="preserve">SU005</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I0826]</t>
+          <t xml:space="preserve">[I5693]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3218,24 +3218,24 @@
         </is>
       </c>
       <c r="C75">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="D75">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">figcaption</t>
+          <t xml:space="preserve">p</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caption</t>
+          <t xml:space="preserve">Body / paragraph</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">[ Photograph: Battersea "A" substation, floodlit — full bleed ]</t>
+          <t xml:space="preserve">Read</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3245,14 +3245,14 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">PH001</t>
+          <t xml:space="preserve">FO002</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I2528]</t>
+          <t xml:space="preserve">[I7693]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="C76">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="D76">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">There is a moment, walking south from the river at dusk, when the substation stops looking like a warning and starts looking like a building. Its transformers hum behind a lattice of steel; a run of ceramic insulators catches the last of the light like a shelf of trophies. Nobody designed it to be beautiful. That, the engineers here will tell you, was the mistake worth fixing.</t>
+          <t xml:space="preserve">Elsewhere</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3288,14 +3288,14 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">AB001</t>
+          <t xml:space="preserve">FO006</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I2532]</t>
+          <t xml:space="preserve">[I0694]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="C77">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D77">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Infrastructure has spent most of a century apologising for itself. We buried the cables, fenced the plant, and planted fast-growing conifers in front of anything that buzzed. The result is a built world we rely on completely and refuse to look at — a landscape of shrugging grey boxes designed, above all, to be ignored.</t>
+          <t xml:space="preserve">Infrastructure, styled to be seen. A fortnightly field guide to the built world.</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">AB002</t>
+          <t xml:space="preserve">FO001</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I2536]</t>
+          <t xml:space="preserve">[I5694]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3347,24 +3347,24 @@
         </is>
       </c>
       <c r="C78">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="D78">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">h2</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heading</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">The case for showing your working</t>
+          <t xml:space="preserve">Latest issue</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3374,14 +3374,14 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">AB010</t>
+          <t xml:space="preserve">FO003</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I2537]</t>
+          <t xml:space="preserve">[I7694]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3390,24 +3390,24 @@
         </is>
       </c>
       <c r="C79">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="D79">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">The counter-movement is small but loud. In three sites across the south-east, engineers and architects have started treating the grid as something to be seen — painting gantries, uplighting cooling towers, cutting viewing slots into perimeter walls. The bill is trivial next to the build. The change in how people treat the thing is not.</t>
+          <t xml:space="preserve">Newsletter</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3417,14 +3417,14 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">AB003</t>
+          <t xml:space="preserve">FO007</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I2750]</t>
+          <t xml:space="preserve">[I5695]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3433,24 +3433,24 @@
         </is>
       </c>
       <c r="C80">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="D80">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">figcaption</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caption</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">[ Photograph: uplit cooling tower, Greenwich reach ]</t>
+          <t xml:space="preserve">Archive</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3460,14 +3460,14 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">PH002</t>
+          <t xml:space="preserve">FO004</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I2552]</t>
+          <t xml:space="preserve">[I7695]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3476,24 +3476,24 @@
         </is>
       </c>
       <c r="C81">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="D81">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">"A fence says keep out. A good facade says look — and people did."</t>
+          <t xml:space="preserve">Instagram</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3503,14 +3503,14 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">PQ001</t>
+          <t xml:space="preserve">FO008</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I2554]</t>
+          <t xml:space="preserve">[I7696]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3519,24 +3519,24 @@
         </is>
       </c>
       <c r="C82">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="D82">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">cite</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Citation</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">— Site engineer, Substation "A"</t>
+          <t xml:space="preserve">Contact</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3546,14 +3546,14 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">PQ002</t>
+          <t xml:space="preserve">FO009</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I2556]</t>
+          <t xml:space="preserve">[I0697]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3562,24 +3562,24 @@
         </is>
       </c>
       <c r="C83">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D83">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">span</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Text</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">What surprised the operators was not the visitors — though there are now visitors — but the vandalism that stopped. A structure people find handsome is a structure people leave alone. Graffiti fell. Fly-tipping at the perimeter fell. The maintenance crews, oddly, reported taking more care too.</t>
+          <t xml:space="preserve">© 2026 ESUNOS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3589,14 +3589,14 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">AB004</t>
+          <t xml:space="preserve">FO010</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I2559]</t>
+          <t xml:space="preserve">[I8697]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3605,24 +3605,24 @@
         </is>
       </c>
       <c r="C84">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="D84">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">h2</t>
+          <t xml:space="preserve">span</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heading</t>
+          <t xml:space="preserve">Text</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Three that got it right</t>
+          <t xml:space="preserve">esunos.com</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3632,40 +3632,40 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">AB011</t>
+          <t xml:space="preserve">FO011</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I2561]</t>
+          <t xml:space="preserve">[O0000]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="C85">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D85">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">title</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Title (SEO)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Below, the shortlist from this issue's field trips — the full notes, drawings and a map are in the members' edition.</t>
+          <t xml:space="preserve">About — ESUNOS</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3675,26 +3675,26 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">AB005</t>
+          <t xml:space="preserve">OX01</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I2963]</t>
+          <t xml:space="preserve">[O0600]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="C86">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D86">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Battersea "A" — floodlighting turned a maintenance liability into the neighbourhood's favourite skyline.</t>
+          <t xml:space="preserve">The ESUNOS Guide to Infrastructure</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3718,26 +3718,26 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">LI001</t>
+          <t xml:space="preserve">OX03</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I2965]</t>
+          <t xml:space="preserve">[O7700]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="C87">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="D87">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Greenwich reach — a perimeter wall with viewing slots, so the plant reads as a colonnade.</t>
+          <t xml:space="preserve">A Network of Newsletters</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3761,40 +3761,40 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">LI002</t>
+          <t xml:space="preserve">OX04</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I2967]</t>
+          <t xml:space="preserve">[O0001]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="C88">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">span</t>
+          <t xml:space="preserve">meta</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Text</t>
+          <t xml:space="preserve">Meta description</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kent interconnector — gantries painted a single confident orange, visible for miles.</t>
+          <t xml:space="preserve">ESUNOS is a network of newsletters about the built world — the substations, spans and server halls we rely on and refuse to notice — and the culture, history and money behind them.</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3804,40 +3804,40 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">LI003</t>
+          <t xml:space="preserve">OX02</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I2779]</t>
+          <t xml:space="preserve">[O6202]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="C89">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="D89">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">figcaption</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caption</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">[ Photograph: Kent interconnector gantries, painted orange ]</t>
+          <t xml:space="preserve">Home</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3847,40 +3847,40 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">PH003</t>
+          <t xml:space="preserve">OX05</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I2580]</t>
+          <t xml:space="preserve">[O6802]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="C90">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="D90">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">None of it is complicated. That is rather the point. The technology of caring what infrastructure looks like is a century old; what was missing was permission. This issue is an argument that the permission is overdue.</t>
+          <t xml:space="preserve">Archive</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3890,40 +3890,40 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">AB006</t>
+          <t xml:space="preserve">OX06</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I0686]</t>
+          <t xml:space="preserve">[O7602]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="C91">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="D91">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subscribe</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3933,40 +3933,40 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">SU001</t>
+          <t xml:space="preserve">OX07</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I0687]</t>
+          <t xml:space="preserve">[O2507]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="C92">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D92">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">h2</t>
+          <t xml:space="preserve">p</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heading</t>
+          <t xml:space="preserve">Body / paragraph</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get the next issue of the Guide to Infrastructure.</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3976,40 +3976,40 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">SU002</t>
+          <t xml:space="preserve">OX08</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I5387]</t>
+          <t xml:space="preserve">[O2508]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="C93">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="D93">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">input</t>
+          <t xml:space="preserve">h1</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Input placeholder</t>
+          <t xml:space="preserve">Page title</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">you@example.com</t>
+          <t xml:space="preserve">Infrastructure is worth looking at on purpose.</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4019,26 +4019,26 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">SU003</t>
+          <t xml:space="preserve">OX09</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I5389]</t>
+          <t xml:space="preserve">[O2514]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="C94">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="D94">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Free. One issue a fortnight. Unsubscribe whenever.</t>
+          <t xml:space="preserve">ESUNOS is a small network of newsletters about the built world — the substations, spans and server halls we rely on and refuse to notice — and the culture, history and money behind them.</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4062,26 +4062,26 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">SU005</t>
+          <t xml:space="preserve">OX10</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I5693]</t>
+          <t xml:space="preserve">[O2520]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="C95">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="D95">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Read</t>
+          <t xml:space="preserve">ESUNOS started as a reaction to a hundred years of hedge-planting. We bury the cables, fence the plant and screen off anything that hums — then act surprised when nobody cares for it. The Guide to Infrastructure is an argument that the opposite is more useful, and a good deal more fun: that a substation, a gantry or a server hall can be a landmark, if anyone bothers to treat it as one.</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4105,26 +4105,26 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">FO002</t>
+          <t xml:space="preserve">OX11</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I7693]</t>
+          <t xml:space="preserve">[O2529]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="C96">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="D96">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsewhere</t>
+          <t xml:space="preserve">So we go and look. Every issue is a field trip — part reportage, part love letter, part quiet argument for building things people are glad to see. We care about the engineering, but just as much about the culture, the history and the money that decide what gets built and what gets buried.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4148,40 +4148,40 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">FO006</t>
+          <t xml:space="preserve">OX12</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I0694]</t>
+          <t xml:space="preserve">[O2535]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="C97">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D97">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">h2</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Heading</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Infrastructure, styled to be seen. A fortnightly field guide to the built world.</t>
+          <t xml:space="preserve">What we cover</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4191,40 +4191,40 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">FO001</t>
+          <t xml:space="preserve">OX13</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I5694]</t>
+          <t xml:space="preserve">[O2537]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="C98">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="D98">
-        <v>94</v>
+        <v>37</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">a</t>
+          <t xml:space="preserve">p</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link</t>
+          <t xml:space="preserve">Body / paragraph</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Latest issue</t>
+          <t xml:space="preserve">Power and the grid. Water and drainage. Transit, roads and the machinery of moving people about. Data centres and the industrial sublime of the internet. Wherever the built world is loud and load-bearing, that is our beat — reported at close range and, where it is warranted, with a straight face abandoned.</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4234,40 +4234,40 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">FO003</t>
+          <t xml:space="preserve">OX14</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I7694]</t>
+          <t xml:space="preserve">[O2544]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="C99">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="D99">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">a</t>
+          <t xml:space="preserve">h2</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link</t>
+          <t xml:space="preserve">Heading</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newsletter</t>
+          <t xml:space="preserve">One masthead, many guides</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4277,40 +4277,40 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">FO007</t>
+          <t xml:space="preserve">OX15</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I5695]</t>
+          <t xml:space="preserve">[O2546]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="C100">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="D100">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">a</t>
+          <t xml:space="preserve">p</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link</t>
+          <t xml:space="preserve">Body / paragraph</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Archive</t>
+          <t xml:space="preserve">ESUNOS is built to be a network. The Guide to Infrastructure is the first title; others will follow, each a field guide to a corner of the world that rewards closer attention. Same masthead, same eye, a different subject each time.</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4320,40 +4320,40 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">FO004</t>
+          <t xml:space="preserve">OX16</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I7695]</t>
+          <t xml:space="preserve">[O2553]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="C101">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="D101">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">a</t>
+          <t xml:space="preserve">h2</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link</t>
+          <t xml:space="preserve">Heading</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instagram</t>
+          <t xml:space="preserve">Masthead</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4363,40 +4363,40 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">FO008</t>
+          <t xml:space="preserve">OX17</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I7696]</t>
+          <t xml:space="preserve">[O2555]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="C102">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="D102">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">a</t>
+          <t xml:space="preserve">dt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link</t>
+          <t xml:space="preserve">Credit label</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contact</t>
+          <t xml:space="preserve">Editor &amp; writer</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4406,40 +4406,40 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">FO009</t>
+          <t xml:space="preserve">OX18</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I0697]</t>
+          <t xml:space="preserve">[O4355]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="C103">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="D103">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">span</t>
+          <t xml:space="preserve">dd</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Text</t>
+          <t xml:space="preserve">Credit value</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">© 2026 ESUNOS</t>
+          <t xml:space="preserve">Hugo Sale</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4449,40 +4449,40 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">FO010</t>
+          <t xml:space="preserve">OX19</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">[I8697]</t>
+          <t xml:space="preserve">[O2558]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue 01</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="C104">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="D104">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">span</t>
+          <t xml:space="preserve">dt</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Text</t>
+          <t xml:space="preserve">Credit label</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">esunos.com</t>
+          <t xml:space="preserve">Published by</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4492,14 +4492,14 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">FO011</t>
+          <t xml:space="preserve">OX20</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O0000]</t>
+          <t xml:space="preserve">[O4358]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4508,24 +4508,24 @@
         </is>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">title</t>
+          <t xml:space="preserve">dd</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Title (SEO)</t>
+          <t xml:space="preserve">Credit value</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">About — ESUNOS</t>
+          <t xml:space="preserve">ESUNOS</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4535,14 +4535,14 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX01</t>
+          <t xml:space="preserve">OX21</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O0600]</t>
+          <t xml:space="preserve">[O2560]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4551,24 +4551,24 @@
         </is>
       </c>
       <c r="C106">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">span</t>
+          <t xml:space="preserve">dt</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Text</t>
+          <t xml:space="preserve">Credit label</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ESUNOS Guide to Infrastructure</t>
+          <t xml:space="preserve">First title</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4578,14 +4578,14 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX03</t>
+          <t xml:space="preserve">OX22</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O7700]</t>
+          <t xml:space="preserve">[O4360]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4594,24 +4594,24 @@
         </is>
       </c>
       <c r="C107">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">span</t>
+          <t xml:space="preserve">dd</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Text</t>
+          <t xml:space="preserve">Credit value</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Network of Newsletters</t>
+          <t xml:space="preserve">The Guide to Infrastructure</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4621,14 +4621,14 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX04</t>
+          <t xml:space="preserve">OX23</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O0001]</t>
+          <t xml:space="preserve">[O4362]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4637,24 +4637,24 @@
         </is>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">meta</t>
+          <t xml:space="preserve">dd</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meta description</t>
+          <t xml:space="preserve">Credit value</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESUNOS is a network of newsletters about the built world — the substations, spans and server halls we rely on and refuse to notice — and the culture, history and money behind them.</t>
+          <t xml:space="preserve">One issue a fortnight, free</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4664,14 +4664,14 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX02</t>
+          <t xml:space="preserve">OX25</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O6202]</t>
+          <t xml:space="preserve">[O2563]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4680,24 +4680,24 @@
         </is>
       </c>
       <c r="C109">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="D109">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">a</t>
+          <t xml:space="preserve">dt</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link</t>
+          <t xml:space="preserve">Credit label</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home</t>
+          <t xml:space="preserve">Cadence</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4707,14 +4707,14 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX05</t>
+          <t xml:space="preserve">OX24</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O6802]</t>
+          <t xml:space="preserve">[O2565]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4723,24 +4723,24 @@
         </is>
       </c>
       <c r="C110">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="D110">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">a</t>
+          <t xml:space="preserve">dt</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link</t>
+          <t xml:space="preserve">Credit label</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Archive</t>
+          <t xml:space="preserve">Based</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4750,14 +4750,14 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX06</t>
+          <t xml:space="preserve">OX26</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O7602]</t>
+          <t xml:space="preserve">[O4365]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4766,24 +4766,24 @@
         </is>
       </c>
       <c r="C111">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="D111">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">a</t>
+          <t xml:space="preserve">dd</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link</t>
+          <t xml:space="preserve">Credit value</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">About</t>
+          <t xml:space="preserve">London, for a global English audience</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4793,14 +4793,14 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX07</t>
+          <t xml:space="preserve">OX27</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O2507]</t>
+          <t xml:space="preserve">[O2567]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4812,21 +4812,21 @@
         <v>25</v>
       </c>
       <c r="D112">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">dt</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Credit label</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">About</t>
+          <t xml:space="preserve">Contact</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4836,14 +4836,14 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX08</t>
+          <t xml:space="preserve">OX28</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O2508]</t>
+          <t xml:space="preserve">[O4367]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4852,24 +4852,24 @@
         </is>
       </c>
       <c r="C113">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D113">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">h1</t>
+          <t xml:space="preserve">dd</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Page title</t>
+          <t xml:space="preserve">Credit value</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Infrastructure is worth looking at on purpose.</t>
+          <t xml:space="preserve">hello@esunos.com</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4879,14 +4879,14 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX09</t>
+          <t xml:space="preserve">OX29</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O2514]</t>
+          <t xml:space="preserve">[O2570]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4898,7 +4898,7 @@
         <v>25</v>
       </c>
       <c r="D114">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESUNOS is a small network of newsletters about the built world — the substations, spans and server halls we rely on and refuse to notice — and the culture, history and money behind them.</t>
+          <t xml:space="preserve">Got a loud local build, a tip, or a title you think ESUNOS should run? We read everything — write to hello@esunos.com.</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4922,14 +4922,14 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX10</t>
+          <t xml:space="preserve">OX30</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O2520]</t>
+          <t xml:space="preserve">[O0676]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="C115">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D115">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESUNOS started as a reaction to a hundred years of hedge-planting. We bury the cables, fence the plant and screen off anything that hums — then act surprised when nobody cares for it. The Guide to Infrastructure is an argument that the opposite is more useful, and a good deal more fun: that a substation, a gantry or a server hall can be a landmark, if anyone bothers to treat it as one.</t>
+          <t xml:space="preserve">Subscribe</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -4965,14 +4965,14 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX11</t>
+          <t xml:space="preserve">OX31</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O2529]</t>
+          <t xml:space="preserve">[O0677]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4981,24 +4981,24 @@
         </is>
       </c>
       <c r="C116">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D116">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">h2</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Body / paragraph</t>
+          <t xml:space="preserve">Heading</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">So we go and look. Every issue is a field trip — part reportage, part love letter, part quiet argument for building things people are glad to see. We care about the engineering, but just as much about the culture, the history and the money that decide what gets built and what gets buried.</t>
+          <t xml:space="preserve">Get the next issue of the Guide to Infrastructure.</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5008,14 +5008,14 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX12</t>
+          <t xml:space="preserve">OX32</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O2535]</t>
+          <t xml:space="preserve">[O5377]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5024,24 +5024,24 @@
         </is>
       </c>
       <c r="C117">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="D117">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">h2</t>
+          <t xml:space="preserve">input</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heading</t>
+          <t xml:space="preserve">Input placeholder</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">What we cover</t>
+          <t xml:space="preserve">you@example.com</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5051,14 +5051,14 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX13</t>
+          <t xml:space="preserve">OX33</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O2537]</t>
+          <t xml:space="preserve">[O5380]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="C118">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="D118">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power and the grid. Water and drainage. Transit, roads and the machinery of moving people about. Data centres and the industrial sublime of the internet. Wherever the built world is loud and load-bearing, that is our beat — reported at close range and, where it is warranted, with a straight face abandoned.</t>
+          <t xml:space="preserve">Free. One issue a fortnight. Unsubscribe whenever.</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5094,14 +5094,14 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX14</t>
+          <t xml:space="preserve">OX34</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O2544]</t>
+          <t xml:space="preserve">[O5688]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5110,24 +5110,24 @@
         </is>
       </c>
       <c r="C119">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="D119">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">h2</t>
+          <t xml:space="preserve">p</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heading</t>
+          <t xml:space="preserve">Body / paragraph</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">One masthead, many guides</t>
+          <t xml:space="preserve">Read</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5137,14 +5137,14 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX15</t>
+          <t xml:space="preserve">OX36</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O2546]</t>
+          <t xml:space="preserve">[O7688]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5153,10 +5153,10 @@
         </is>
       </c>
       <c r="C120">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="D120">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESUNOS is built to be a network. The Guide to Infrastructure is the first title; others will follow, each a field guide to a corner of the world that rewards closer attention. Same masthead, same eye, a different subject each time.</t>
+          <t xml:space="preserve">Elsewhere</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5180,14 +5180,14 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX16</t>
+          <t xml:space="preserve">OX40</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O2553]</t>
+          <t xml:space="preserve">[O5689]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5196,24 +5196,24 @@
         </is>
       </c>
       <c r="C121">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="D121">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">h2</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heading</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Masthead</t>
+          <t xml:space="preserve">Latest issue</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5223,14 +5223,14 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX17</t>
+          <t xml:space="preserve">OX37</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O2555]</t>
+          <t xml:space="preserve">[O7689]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5239,24 +5239,24 @@
         </is>
       </c>
       <c r="C122">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="D122">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">dt</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Credit label</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Editor &amp; writer</t>
+          <t xml:space="preserve">Newsletter</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5266,14 +5266,14 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX18</t>
+          <t xml:space="preserve">OX41</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O4355]</t>
+          <t xml:space="preserve">[O0690]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5282,24 +5282,24 @@
         </is>
       </c>
       <c r="C123">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="D123">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">dd</t>
+          <t xml:space="preserve">p</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Credit value</t>
+          <t xml:space="preserve">Body / paragraph</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hugo Sale</t>
+          <t xml:space="preserve">Infrastructure, styled to be seen. A fortnightly field guide to the built world.</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5309,14 +5309,14 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX19</t>
+          <t xml:space="preserve">OX35</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O2558]</t>
+          <t xml:space="preserve">[O5691]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5325,24 +5325,24 @@
         </is>
       </c>
       <c r="C124">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="D124">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">dt</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Credit label</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Published by</t>
+          <t xml:space="preserve">Archive</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5352,14 +5352,14 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX20</t>
+          <t xml:space="preserve">OX38</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O4358]</t>
+          <t xml:space="preserve">[O7691]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5368,24 +5368,24 @@
         </is>
       </c>
       <c r="C125">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="D125">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">dd</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Credit value</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESUNOS</t>
+          <t xml:space="preserve">Instagram</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5395,14 +5395,14 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX21</t>
+          <t xml:space="preserve">OX42</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O2560]</t>
+          <t xml:space="preserve">[O5692]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5411,24 +5411,24 @@
         </is>
       </c>
       <c r="C126">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="D126">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">dt</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Credit label</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">First title</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5438,14 +5438,14 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX22</t>
+          <t xml:space="preserve">OX39</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O4360]</t>
+          <t xml:space="preserve">[O7692]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5454,24 +5454,24 @@
         </is>
       </c>
       <c r="C127">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="D127">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">dd</t>
+          <t xml:space="preserve">a</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Credit value</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Guide to Infrastructure</t>
+          <t xml:space="preserve">Contact</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5481,14 +5481,14 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX23</t>
+          <t xml:space="preserve">OX43</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O4362]</t>
+          <t xml:space="preserve">[O0696]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5497,24 +5497,24 @@
         </is>
       </c>
       <c r="C128">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="D128">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">dd</t>
+          <t xml:space="preserve">span</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Credit value</t>
+          <t xml:space="preserve">Text</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">One issue a fortnight, free</t>
+          <t xml:space="preserve">© 2026 ESUNOS</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5524,14 +5524,14 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX25</t>
+          <t xml:space="preserve">OX44</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">[O2563]</t>
+          <t xml:space="preserve">[O8696]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5540,24 +5540,24 @@
         </is>
       </c>
       <c r="C129">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="D129">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">dt</t>
+          <t xml:space="preserve">span</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Credit label</t>
+          <t xml:space="preserve">Text</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cadence</t>
+          <t xml:space="preserve">esunos.com</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5566,866 +5566,6 @@
         </is>
       </c>
       <c r="I129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX24</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[O2565]</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="C130">
-        <v>25</v>
-      </c>
-      <c r="D130">
-        <v>65</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dt</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Credit label</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Based</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX26</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[O4365]</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="C131">
-        <v>43</v>
-      </c>
-      <c r="D131">
-        <v>65</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dd</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Credit value</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">London, for a global English audience</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX27</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[O2567]</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="C132">
-        <v>25</v>
-      </c>
-      <c r="D132">
-        <v>67</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dt</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Credit label</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contact</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX28</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[O4367]</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="C133">
-        <v>43</v>
-      </c>
-      <c r="D133">
-        <v>67</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dd</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Credit value</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hello@esunos.com</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX29</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[O2570]</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="C134">
-        <v>25</v>
-      </c>
-      <c r="D134">
-        <v>70</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Body / paragraph</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Got a loud local build, a tip, or a title you think ESUNOS should run? We read everything — write to hello@esunos.com.</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX30</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[O0676]</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="C135">
-        <v>6</v>
-      </c>
-      <c r="D135">
-        <v>76</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Body / paragraph</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Subscribe</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX31</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[O0677]</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="C136">
-        <v>6</v>
-      </c>
-      <c r="D136">
-        <v>77</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">h2</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heading</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Get the next issue of the Guide to Infrastructure.</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX32</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[O5377]</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="C137">
-        <v>53</v>
-      </c>
-      <c r="D137">
-        <v>77</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">input</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Input placeholder</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">you@example.com</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX33</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[O5380]</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="C138">
-        <v>53</v>
-      </c>
-      <c r="D138">
-        <v>80</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Body / paragraph</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Free. One issue a fortnight. Unsubscribe whenever.</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX34</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[O5688]</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="C139">
-        <v>56</v>
-      </c>
-      <c r="D139">
-        <v>88</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Body / paragraph</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Read</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX36</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[O7688]</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="C140">
-        <v>76</v>
-      </c>
-      <c r="D140">
-        <v>88</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Body / paragraph</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Elsewhere</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX40</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[O5689]</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="C141">
-        <v>56</v>
-      </c>
-      <c r="D141">
-        <v>89</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Link</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Latest issue</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX37</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[O7689]</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="C142">
-        <v>76</v>
-      </c>
-      <c r="D142">
-        <v>89</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Link</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Newsletter</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX41</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[O0690]</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="C143">
-        <v>6</v>
-      </c>
-      <c r="D143">
-        <v>90</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Body / paragraph</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Infrastructure, styled to be seen. A fortnightly field guide to the built world.</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX35</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[O5691]</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="C144">
-        <v>56</v>
-      </c>
-      <c r="D144">
-        <v>91</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Link</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Archive</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX38</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[O7691]</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="C145">
-        <v>76</v>
-      </c>
-      <c r="D145">
-        <v>91</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Link</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Instagram</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX42</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[O5692]</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="C146">
-        <v>56</v>
-      </c>
-      <c r="D146">
-        <v>92</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Link</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX39</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[O7692]</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="C147">
-        <v>76</v>
-      </c>
-      <c r="D147">
-        <v>92</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Link</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contact</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX43</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[O0696]</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="C148">
-        <v>6</v>
-      </c>
-      <c r="D148">
-        <v>96</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">span</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Text</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">© 2026 ESUNOS</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX44</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[O8696]</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">About</t>
-        </is>
-      </c>
-      <c r="C149">
-        <v>86</v>
-      </c>
-      <c r="D149">
-        <v>96</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">span</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Text</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">esunos.com</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
         <is>
           <t xml:space="preserve">OX45</t>
         </is>
